--- a/applications/METFORMIN-HIIE_study/positive/pos_lipid_reference_set.xlsx
+++ b/applications/METFORMIN-HIIE_study/positive/pos_lipid_reference_set.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/applications/exercise_study/positive/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/applications/METFORMIN-HIIE_study/positive/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1274529A-D068-BF4B-87FF-4B33CEDB3DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9BC2DD7-EB5A-3E4B-A2AE-FB70E26FA2F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="14680" windowHeight="17400" xr2:uid="{9E5E902E-872A-BE45-A1A9-54571E2C3B45}"/>
   </bookViews>
@@ -36,13 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
-  <si>
-    <t>CAR (5:0)</t>
-  </si>
-  <si>
-    <t>LPC (20:0)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
   <si>
     <t>SM</t>
   </si>
@@ -101,18 +95,12 @@
     <t>C17 Sphinganine</t>
   </si>
   <si>
-    <t>Light</t>
-  </si>
-  <si>
     <t>Cer(d40:2)</t>
   </si>
   <si>
     <t>Cer</t>
   </si>
   <si>
-    <t>ISTD</t>
-  </si>
-  <si>
     <t>Sphinganine</t>
   </si>
   <si>
@@ -156,6 +144,21 @@
   </si>
   <si>
     <t>SM_2</t>
+  </si>
+  <si>
+    <t>CAR(5:0)</t>
+  </si>
+  <si>
+    <t>LPC(20:0)</t>
+  </si>
+  <si>
+    <t>IS</t>
+  </si>
+  <si>
+    <t>LightSplash</t>
+  </si>
+  <si>
+    <t>HexCer(d18:1/24:0)</t>
   </si>
 </sst>
 </file>
@@ -584,30 +587,30 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C2" s="3">
         <v>246.17</v>
@@ -619,17 +622,17 @@
         <v>48</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C3" s="3">
         <v>496.33980000000003</v>
@@ -641,17 +644,17 @@
         <v>153.6</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="C4" s="3">
         <v>552.40239999999994</v>
@@ -663,17 +666,17 @@
         <v>254.4</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3">
         <v>701.55920000000003</v>
@@ -685,17 +688,17 @@
         <v>371.40000000000003</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C6" s="3">
         <v>758.56939999999997</v>
@@ -707,17 +710,17 @@
         <v>465.59999999999997</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3">
         <v>759.63879999999995</v>
@@ -729,17 +732,17 @@
         <v>685.8</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="C8" s="3">
         <v>812.69740000000002</v>
@@ -751,17 +754,17 @@
         <v>735</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C9" s="3">
         <v>900.80150000000003</v>
@@ -773,17 +776,17 @@
         <v>838.2</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3">
         <v>880.83274340259902</v>
@@ -795,17 +798,17 @@
         <v>963</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C11" s="2">
         <v>678.65070000000003</v>
@@ -817,17 +820,17 @@
         <v>720</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C12" s="8">
         <v>522.35540000000003</v>
@@ -839,17 +842,17 @@
         <v>157.20000000000002</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C13" s="8">
         <v>522.35540000000003</v>
@@ -861,17 +864,17 @@
         <v>168</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C14" s="8">
         <v>480.30849999999998</v>
@@ -883,17 +886,17 @@
         <v>174</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C15" s="8">
         <v>480.30849999999998</v>
@@ -905,17 +908,17 @@
         <v>165</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C16" s="8">
         <v>729.59050000000002</v>
@@ -927,16 +930,16 @@
         <v>466.2</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G16" s="3"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C17" s="2">
         <v>288.28969999999998</v>
@@ -948,7 +951,7 @@
         <v>119.4</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G17" s="3"/>
     </row>
